--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table20.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table20.xlsx
@@ -515,16 +515,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -534,6 +528,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -543,10 +543,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -856,7 +856,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1848,24 +1848,24 @@
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="49" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:63" ht="20.149999999999999" customHeight="1">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="55" t="s">
@@ -1882,12 +1882,12 @@
       <c r="K4" s="56"/>
       <c r="L4" s="56"/>
       <c r="M4" s="57"/>
-      <c r="N4" s="58" t="s">
+      <c r="N4" s="53" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:63" ht="54.75" customHeight="1">
-      <c r="A5" s="51"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="59"/>
+      <c r="N5" s="54"/>
       <c r="O5" s="7"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -2926,7 +2926,7 @@
       <c r="R25" s="13"/>
     </row>
     <row r="26" spans="1:18" ht="30" customHeight="1">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="50" t="s">
         <v>5</v>
       </c>
       <c r="B26" s="31">
@@ -2988,7 +2988,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="30" customHeight="1">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="51" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="35">
@@ -3049,7 +3049,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="30" customHeight="1">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="51" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="36">
@@ -3110,7 +3110,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="30" customHeight="1">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="51" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="37">
@@ -3172,7 +3172,7 @@
       <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="1:18" ht="30" customHeight="1">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="52" t="s">
         <v>41</v>
       </c>
       <c r="B30" s="39">
